--- a/Methodology/PIRNN/03-PWM-X/Ts-03/Resumo_Estatisticas.xlsx
+++ b/Methodology/PIRNN/03-PWM-X/Ts-03/Resumo_Estatisticas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Todos_Modelos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Top_10_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Top_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Melhor_Modelo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,16 +474,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.119490883358185</v>
+        <v>-0.111040245625267</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7182042957856348</v>
+        <v>0.6832113298459535</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1207099206182536</v>
+        <v>0.1197987244441015</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07744090177126933</v>
+        <v>0.07366775970859769</v>
       </c>
     </row>
     <row r="3">
@@ -497,16 +498,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-7.323796487385374</v>
+        <v>-7.144614426278395</v>
       </c>
       <c r="D3" t="n">
-        <v>5.223316303635442</v>
+        <v>4.972873295367428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7013659201145148</v>
+        <v>0.6862679787668658</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4401184064147108</v>
+        <v>0.4190159934477021</v>
       </c>
     </row>
     <row r="4">
@@ -521,16 +522,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.08785183515563003</v>
+        <v>-0.08634338959035458</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9746256527278501</v>
+        <v>0.9842337194665335</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1040237980836577</v>
+        <v>0.1038795557963981</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09319675605640794</v>
+        <v>0.09411550947677251</v>
       </c>
     </row>
     <row r="5">
@@ -545,16 +546,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.1289327875297934</v>
+        <v>-0.1166706350652096</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7078902625242773</v>
+        <v>0.6658911612829613</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182677027725072</v>
+        <v>0.1169831120341996</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07415902531005536</v>
+        <v>0.06975917327529522</v>
       </c>
     </row>
     <row r="6">
@@ -569,16 +570,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-7.099261591728506</v>
+        <v>-6.915243106426655</v>
       </c>
       <c r="D6" t="n">
-        <v>5.242591396526085</v>
+        <v>4.954646753724418</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6665142325995139</v>
+        <v>0.6513707607995234</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4314296731762517</v>
+        <v>0.407733784303605</v>
       </c>
     </row>
     <row r="7">
@@ -593,16 +594,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7376828814674506</v>
+        <v>0.7297675122613333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2673709376701043</v>
+        <v>0.2982605516949753</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02413432237067391</v>
+        <v>0.02486257096219555</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02459929583847944</v>
+        <v>0.02744127545060842</v>
       </c>
     </row>
   </sheetData>
@@ -663,16 +664,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6346267299433898</v>
+        <v>0.7101285353349645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2276295687617187</v>
+        <v>0.06303116960943746</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03939663920465701</v>
+        <v>0.031255601996732</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0245443241959863</v>
+        <v>0.006796381813496657</v>
       </c>
     </row>
     <row r="3">
@@ -687,16 +688,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-9.541000410319162</v>
+        <v>-1.315961464966486</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1806931535799398</v>
+        <v>0.3029385096969688</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8881882759766102</v>
+        <v>0.1951436999075654</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01522526651282847</v>
+        <v>0.02552570175324824</v>
       </c>
     </row>
     <row r="4">
@@ -711,16 +712,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9581119520637795</v>
+        <v>0.958747482376445</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007400814524782934</v>
+        <v>0.003624814884831982</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004005466277503311</v>
+        <v>0.003944694879428412</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007076890536940475</v>
+        <v>0.0003466161470568781</v>
       </c>
     </row>
     <row r="5">
@@ -735,16 +736,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7203498457730585</v>
+        <v>0.7410637353883189</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03722965190832744</v>
+        <v>0.05227253996679147</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02929632453386856</v>
+        <v>0.02712632454153908</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003900201548625652</v>
+        <v>0.005476103881687772</v>
       </c>
     </row>
     <row r="6">
@@ -759,16 +760,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-9.465279524788064</v>
+        <v>-1.17568652300075</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2477104706695735</v>
+        <v>0.3084416519340469</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8612214425234901</v>
+        <v>0.1790442272831282</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0203848897081937</v>
+        <v>0.02538265354344156</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +784,207 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9640065154222313</v>
+        <v>0.9692914460193544</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002418883721003767</v>
+        <v>0.005448704265510492</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003311558029088236</v>
+        <v>0.002825321296041078</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00022254788336521</v>
+        <v>0.0005013046269413777</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Neurons</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Best_R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>model_264_Ld0.3_Lp0.7_r0.9_seed4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[264]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8827413342605187</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>model_264_128_64_Ld0.5_Lp0.5_r0.01_seed4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[264, 128, 64]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.5577356708241645</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>model_264_128_64_Ld0.7_Lp0.3_r0.9_seed1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[264, 128, 64]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.965761194833384</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>model_264_Ld0.3_Lp0.7_r0.9_seed4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[264]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8685234112721839</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Test_2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>model_264_128_64_Ld0.5_Lp0.5_r0.01_seed4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[264, 128, 64]</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.4163799993432535</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Test_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>model_8_4_Ld0.7_Lp0.3_r0.5_seed2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[8, 4]</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9801624128293442</v>
       </c>
     </row>
   </sheetData>
